--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N156_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N156_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.52596558781223</v>
+        <v>10.16046940801949</v>
       </c>
       <c r="D2" t="n">
-        <v>22.17557069723973</v>
+        <v>3.603530238301456</v>
       </c>
       <c r="E2" t="n">
-        <v>13.23993310335319</v>
+        <v>2.151489129294893</v>
       </c>
       <c r="F2" t="n">
-        <v>9.929464891194389</v>
+        <v>1.613538044819088</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.91872989871507</v>
+        <v>4.8617936085412</v>
       </c>
       <c r="D3" t="n">
-        <v>33.02763841562346</v>
+        <v>5.366991242538812</v>
       </c>
       <c r="E3" t="n">
-        <v>13.23993310335319</v>
+        <v>2.151489129294893</v>
       </c>
       <c r="F3" t="n">
-        <v>9.929464891194389</v>
+        <v>1.613538044819088</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.57658382257485</v>
+        <v>6.106194871168412</v>
       </c>
       <c r="D4" t="n">
-        <v>10.29456934361506</v>
+        <v>1.672867518337448</v>
       </c>
       <c r="E4" t="n">
-        <v>13.23993310335319</v>
+        <v>2.151489129294893</v>
       </c>
       <c r="F4" t="n">
-        <v>9.929464891194389</v>
+        <v>1.613538044819088</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.18937160831231</v>
+        <v>7.34327288635075</v>
       </c>
       <c r="D5" t="n">
-        <v>38.81043674065006</v>
+        <v>6.306695970355635</v>
       </c>
       <c r="E5" t="n">
-        <v>13.23993310335319</v>
+        <v>2.151489129294893</v>
       </c>
       <c r="F5" t="n">
-        <v>9.929464891194389</v>
+        <v>1.613538044819088</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.28397173851811</v>
+        <v>5.246145407509194</v>
       </c>
       <c r="D6" t="n">
-        <v>10.83461530876333</v>
+        <v>1.760624987674042</v>
       </c>
       <c r="E6" t="n">
-        <v>13.23993310335319</v>
+        <v>2.151489129294893</v>
       </c>
       <c r="F6" t="n">
-        <v>9.929464891194389</v>
+        <v>1.613538044819088</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.1639686601285</v>
+        <v>5.389144907270881</v>
       </c>
       <c r="D7" t="n">
-        <v>26.05534428727789</v>
+        <v>4.233993446682657</v>
       </c>
       <c r="E7" t="n">
-        <v>13.23993310335319</v>
+        <v>2.151489129294893</v>
       </c>
       <c r="F7" t="n">
-        <v>9.929464891194389</v>
+        <v>1.613538044819088</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.95735618162524</v>
+        <v>6.655570379514101</v>
       </c>
       <c r="D8" t="n">
-        <v>21.46489322124742</v>
+        <v>3.488045148452705</v>
       </c>
       <c r="E8" t="n">
-        <v>13.23993310335319</v>
+        <v>2.151489129294893</v>
       </c>
       <c r="F8" t="n">
-        <v>9.929464891194389</v>
+        <v>1.613538044819088</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.33418854341103</v>
+        <v>8.829305638304293</v>
       </c>
       <c r="D9" t="n">
-        <v>32.70289480616005</v>
+        <v>5.314220406001009</v>
       </c>
       <c r="E9" t="n">
-        <v>13.23993310335319</v>
+        <v>2.151489129294893</v>
       </c>
       <c r="F9" t="n">
-        <v>9.929464891194389</v>
+        <v>1.613538044819088</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.8492424049175</v>
+        <v>2.413001890799094</v>
       </c>
       <c r="D10" t="n">
-        <v>12.00462873691274</v>
+        <v>1.95075216974832</v>
       </c>
       <c r="E10" t="n">
-        <v>13.23993310335319</v>
+        <v>2.151489129294893</v>
       </c>
       <c r="F10" t="n">
-        <v>9.929464891194389</v>
+        <v>1.613538044819088</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
